--- a/samples/K_科目余额表.xlsx
+++ b/samples/K_科目余额表.xlsx
@@ -438,11 +438,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -508,19 +508,79 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>800000</v>
+        <v>1200000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2400000</v>
+        <v>1800000</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>应付票据-银承</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>1200000</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>220102</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>应付票据-商承</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>500000</v>
       </c>
     </row>
   </sheetData>

--- a/samples/K_科目余额表.xlsx
+++ b/samples/K_科目余额表.xlsx
@@ -442,7 +442,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
